--- a/MSME/MSME intrim claim calculations.xlsx
+++ b/MSME/MSME intrim claim calculations.xlsx
@@ -2,13 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Intrim claim" sheetId="3" r:id="rId1"/>
-    <sheet name="Final claim" sheetId="2" r:id="rId2"/>
+    <sheet name="Intrim claim(OTS=N)" sheetId="3" r:id="rId1"/>
+    <sheet name="Intrim claim (OTS=Y)" sheetId="5" r:id="rId2"/>
+    <sheet name="Final claim(OTS=N)" sheetId="2" r:id="rId3"/>
+    <sheet name="Final claim(OTS=Y)" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="204">
   <si>
     <t>S. No.</t>
   </si>
@@ -286,6 +288,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">This field is editable to NCGTC users while settlement of claims. </t>
     </r>
     <r>
@@ -321,6 +330,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">This field is editable to NCGTC users while settlement of claims.   </t>
     </r>
     <r>
@@ -501,6 +517,18 @@
     <t>Auto-calc. If 29&lt;23 then 23-29</t>
   </si>
   <si>
+    <t>Formula MLI side</t>
+  </si>
+  <si>
+    <t>Formula NCGTC side</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Ediatble</t>
+  </si>
+  <si>
     <t>Dropdown Option</t>
   </si>
   <si>
@@ -569,6 +597,9 @@
   </si>
   <si>
     <t>Mandatory , if OTS = No</t>
+  </si>
+  <si>
+    <t>Editable</t>
   </si>
   <si>
     <t>17A</t>
@@ -704,7 +735,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,29 +766,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -907,7 +916,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -935,6 +944,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1278,137 +1293,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1448,43 +1463,40 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2011,787 +2023,790 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="13" customWidth="1"/>
-    <col min="2" max="2" width="38" style="13" customWidth="1"/>
-    <col min="3" max="3" width="64" style="13" customWidth="1"/>
-    <col min="4" max="4" width="48.2857142857143" style="13" customWidth="1"/>
-    <col min="5" max="5" width="34.2857142857143" style="13" customWidth="1"/>
-    <col min="6" max="6" width="21.2857142857143" style="14" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="14" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="14" customWidth="1"/>
+    <col min="2" max="2" width="38" style="14" customWidth="1"/>
+    <col min="3" max="3" width="64" style="14" customWidth="1"/>
+    <col min="4" max="4" width="48.2857142857143" style="14" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="14" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="15" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="15" customWidth="1"/>
     <col min="8" max="9" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="E2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" ht="30" spans="1:8">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="E3" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="E4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="E5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
     </row>
     <row r="6" ht="30" spans="1:8">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="E6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" ht="30" spans="1:8">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="E7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="18" t="s">
+      <c r="E8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:8">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
     </row>
     <row r="11" ht="30" spans="1:8">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" ht="30" spans="1:8">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
     </row>
     <row r="13" ht="30" spans="1:8">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" ht="30" spans="1:8">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="18">
-        <v>150000000</v>
-      </c>
-      <c r="G15" s="18" t="s">
+      <c r="E15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="19">
+        <v>50000000</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="21"/>
+      <c r="H15" s="22"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="22">
-        <v>10000</v>
-      </c>
-      <c r="G16" s="18" t="s">
+      <c r="E16" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="10">
+        <v>60000000</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="21"/>
+      <c r="H16" s="22"/>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="18">
+      <c r="E17" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="19">
         <f>MAX(F15,F16)</f>
-        <v>150000000</v>
-      </c>
-      <c r="G17" s="18" t="s">
+        <v>60000000</v>
+      </c>
+      <c r="G17" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="21"/>
+      <c r="H17" s="22"/>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="18">
-        <v>400000001</v>
-      </c>
-      <c r="G18" s="18" t="s">
+      <c r="E18" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="19">
+        <v>100000000</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="21"/>
+      <c r="H18" s="22"/>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="18">
-        <v>5000001</v>
-      </c>
-      <c r="G19" s="18" t="s">
+      <c r="E19" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="19">
+        <v>100000000</v>
+      </c>
+      <c r="G19" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="21"/>
+      <c r="H19" s="22"/>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="22">
-        <v>2000</v>
-      </c>
-      <c r="G20" s="18" t="s">
+      <c r="F20" s="10">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="21"/>
+      <c r="H20" s="22"/>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="18">
+      <c r="E21" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="19">
         <f>F18</f>
-        <v>400000001</v>
-      </c>
-      <c r="G21" s="18" t="s">
+        <v>100000000</v>
+      </c>
+      <c r="G21" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H21" s="8"/>
     </row>
     <row r="22" ht="30" spans="1:10">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="18">
+      <c r="E22" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="19">
         <f>F19</f>
-        <v>5000001</v>
-      </c>
-      <c r="G22" s="18" t="s">
+        <v>100000000</v>
+      </c>
+      <c r="G22" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H22" s="8"/>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <f>F20</f>
-        <v>2000</v>
-      </c>
-      <c r="G23" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H23" s="8"/>
     </row>
     <row r="24" ht="120" spans="1:10">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="18">
+      <c r="E24" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="19">
         <f>IF(F8="N",F18+F19-F20,IF(F8="Y",F18+F19-F13,""))</f>
-        <v>404998002</v>
-      </c>
-      <c r="G24" s="18" t="s">
+        <v>200000000</v>
+      </c>
+      <c r="G24" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="24"/>
+      <c r="H24" s="23"/>
       <c r="I24">
         <f>IF(F8="N",F21+F22-F23,IF(F8="Y",F21+F22-F13,""))</f>
-        <v>404998002</v>
+        <v>200000000</v>
       </c>
       <c r="J24" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="18">
+      <c r="E25" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="19">
         <f>60%*(F24-F17)</f>
-        <v>152998801.2</v>
-      </c>
-      <c r="G25" s="18" t="s">
+        <v>84000000</v>
+      </c>
+      <c r="G25" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="24"/>
+      <c r="H25" s="23"/>
     </row>
     <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="18">
+      <c r="E26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="19">
         <f>IF(F8="N",75%*F25,IF(F8="Y",100%*F25,""))</f>
-        <v>114749100.9</v>
-      </c>
-      <c r="G26" s="18" t="s">
+        <v>63000000</v>
+      </c>
+      <c r="G26" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="24"/>
+      <c r="H26" s="23"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="18">
-        <v>556932624</v>
-      </c>
-      <c r="G27" s="18" t="s">
+      <c r="E27" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="19">
+        <v>5487293.76</v>
+      </c>
+      <c r="G27" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="24"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" ht="45" spans="1:10">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="18">
+      <c r="E28" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="19">
         <v>0</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="24"/>
+      <c r="H28" s="23"/>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="18">
+      <c r="E29" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="19">
         <f>2*(F27+F28)</f>
-        <v>1113865248</v>
-      </c>
-      <c r="G29" s="18" t="s">
+        <v>10974587.52</v>
+      </c>
+      <c r="G29" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="24"/>
+      <c r="H29" s="23"/>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="22">
+      <c r="E30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="10">
         <v>0</v>
       </c>
-      <c r="G30" s="18"/>
-      <c r="H30" s="24"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="23"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="19">
         <f>F29-F30</f>
-        <v>1113865248</v>
-      </c>
-      <c r="G31" s="18" t="s">
+        <v>10974587.52</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="24"/>
+      <c r="H31" s="23"/>
     </row>
     <row r="32" ht="60" spans="1:10">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="18">
+      <c r="E32" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="19">
         <f>IF(F26&lt;=F31,F26,F31)</f>
-        <v>114749100.9</v>
-      </c>
-      <c r="G32" s="18" t="s">
+        <v>10974587.52</v>
+      </c>
+      <c r="G32" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="24"/>
+      <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="18">
+      <c r="E33" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="19">
         <f>F31-F32</f>
-        <v>999116147.1</v>
-      </c>
-      <c r="G33" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="24"/>
+      <c r="H33" s="23"/>
     </row>
     <row r="34" ht="30" spans="1:8">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18" t="s">
+      <c r="E34" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="19">
+        <f>IF(F32&lt;F26,F26-F32)</f>
+        <v>52025412.48</v>
+      </c>
+      <c r="G34" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="24"/>
+      <c r="H34" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2801,7 +2816,1700 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.4190476190476" style="13" customWidth="1"/>
+    <col min="2" max="2" width="38" style="14" customWidth="1"/>
+    <col min="3" max="3" width="64" style="14" customWidth="1"/>
+    <col min="4" max="4" width="39.6571428571429" style="14" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="14" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="15" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="15" customWidth="1"/>
+    <col min="8" max="8" width="9.4" customWidth="1"/>
+    <col min="9" max="9" width="21.2857142857143" style="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" ht="30" spans="1:10">
+      <c r="A3" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="I3" s="19"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" ht="30" spans="1:10">
+      <c r="A6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" ht="30" spans="1:10">
+      <c r="A7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="19" t="str">
+        <f>F8</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="9" ht="30" spans="1:10">
+      <c r="A9" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="19">
+        <v>10000</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="I10" s="19">
+        <f>F10</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:10">
+      <c r="A11" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="19">
+        <f>F10</f>
+        <v>10000</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="I11" s="19">
+        <f>F11</f>
+        <v>10000</v>
+      </c>
+      <c r="J11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" ht="30" spans="1:10">
+      <c r="A12" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="19">
+        <v>2000</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="I12" s="19">
+        <f>F12</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:10">
+      <c r="A13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="19">
+        <f>40%*(F10-F12)</f>
+        <v>3200</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="I13" s="19">
+        <f>40%*(I11-I12)</f>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:10">
+      <c r="A14" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="19">
+        <f>60%*(F10-F12)</f>
+        <v>4800</v>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="I14" s="19">
+        <f>60%*(I10-I12)</f>
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="19">
+        <v>50000000</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="19">
+        <f>F15</f>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="10">
+        <v>60000000</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="10">
+        <f>F16</f>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="17" ht="30" spans="1:10">
+      <c r="A17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="19">
+        <f>MAX(F15,F16)</f>
+        <v>60000000</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="19">
+        <f>MAX(I15,I16)</f>
+        <v>60000000</v>
+      </c>
+    </row>
+    <row r="18" ht="30" spans="1:10">
+      <c r="A18" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="19">
+        <v>200000000</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="19">
+        <f>F18</f>
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:10">
+      <c r="A19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="19">
+        <v>200000000</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="19">
+        <f>F19</f>
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="1:10">
+      <c r="A20" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="19">
+        <f>F18</f>
+        <v>200000000</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="19">
+        <f>F20</f>
+        <v>200000000</v>
+      </c>
+      <c r="J20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:10">
+      <c r="A21" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="19">
+        <f>F19</f>
+        <v>200000000</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="19">
+        <f>F21</f>
+        <v>200000000</v>
+      </c>
+      <c r="J21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" ht="120" spans="1:10">
+      <c r="A22" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="19">
+        <f>IF(F8="N",F18+F19-#REF!,IF(F8="Y",F18+F19-F13,""))</f>
+        <v>399996800</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="23"/>
+      <c r="I22" s="19">
+        <f>IF(I8="N",I18+I19-#REF!,IF(I8="Y",I18+I19-I13,""))</f>
+        <v>399996800</v>
+      </c>
+    </row>
+    <row r="23" ht="30" spans="1:10">
+      <c r="A23" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="19">
+        <f>60%*(F22-F17)</f>
+        <v>203998080</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="23"/>
+      <c r="I23" s="19">
+        <f>60%*(I22-I17)</f>
+        <v>203998080</v>
+      </c>
+    </row>
+    <row r="24" ht="45" spans="1:10">
+      <c r="A24" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="19">
+        <f>IF(F8="N",75%*F23,IF(F8="Y",100%*F23,""))</f>
+        <v>203998080</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="23"/>
+      <c r="I24" s="19">
+        <f>IF(I8="N",75%*I23,IF(I8="Y",100%*I23,""))</f>
+        <v>203998080</v>
+      </c>
+    </row>
+    <row r="25" ht="30" spans="1:10">
+      <c r="A25" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="23"/>
+      <c r="I25" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="45" spans="1:10">
+      <c r="A26" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="23"/>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:10">
+      <c r="A27" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="19">
+        <f>2*(F25+F26)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="19">
+        <f>2*(I25+I26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="30" spans="1:10">
+      <c r="A28" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="10">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="19">
+        <f>F27-F28</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29" s="23"/>
+      <c r="I29" s="19">
+        <f>I27-I28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="60" spans="1:10">
+      <c r="A30" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="19">
+        <f>IF(F24&lt;=F29,F24,F29)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="23"/>
+      <c r="I30" s="19">
+        <f>IF(I24&lt;=I29,I24,I29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="19">
+        <f>F29-F30</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" s="23"/>
+      <c r="I31" s="19">
+        <f>I29-I30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:10">
+      <c r="A32" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="23"/>
+      <c r="I32" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:K39"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.71428571428571" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5714285714286" style="1" customWidth="1"/>
+    <col min="3" max="3" width="49.1428571428571" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42.2857142857143" style="1" customWidth="1"/>
+    <col min="5" max="5" width="31.4285714285714" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.2857142857143" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.8571428571429" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.57142857142857"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" ht="30" spans="1:11">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="J5" t="s">
+        <v>144</v>
+      </c>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" ht="75" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="J6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" ht="45" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" ht="30" spans="1:11">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" ht="45" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" ht="45" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" ht="30" spans="1:11">
+      <c r="A14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" ht="60" spans="1:11">
+      <c r="A15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" ht="45" spans="1:11">
+      <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="6">
+        <v>100000000</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" ht="30" spans="1:10">
+      <c r="A17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="6">
+        <v>10</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" ht="45" spans="1:10">
+      <c r="A18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="6">
+        <v>80000000</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" ht="45" spans="1:10">
+      <c r="A19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="6">
+        <f>F18</f>
+        <v>80000000</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="I19">
+        <f>F19</f>
+        <v>80000000</v>
+      </c>
+      <c r="J19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" ht="45" spans="1:10">
+      <c r="A20" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="6">
+        <f>40%*F18</f>
+        <v>32000000</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="I20">
+        <f>40%*I19</f>
+        <v>32000000</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:10">
+      <c r="A21" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="6">
+        <f>60%*F18</f>
+        <v>48000000</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="I21">
+        <f>60%*I19</f>
+        <v>48000000</v>
+      </c>
+    </row>
+    <row r="22" ht="60" spans="1:10">
+      <c r="A22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="6">
+        <v>50000000</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="5">
+        <v>60000000</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="6">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" ht="30" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="6">
+        <f>MAX(F24,F25)</f>
+        <v>60000000</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" ht="120" spans="1:10">
+      <c r="A28" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="6">
+        <f>F15+F16-F17-F20</f>
+        <v>167999990</v>
+      </c>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" ht="30" spans="1:10">
+      <c r="A29" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" ht="30" spans="1:10">
+      <c r="A30" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" ht="30" spans="1:10">
+      <c r="A32" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" ht="30" spans="1:7">
+      <c r="A33" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" ht="30" spans="1:7">
+      <c r="A34" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" ht="45" spans="1:7">
+      <c r="A37" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" ht="30" spans="1:7">
+      <c r="A39" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
@@ -2848,7 +4556,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>11</v>
@@ -2864,7 +4572,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>15</v>
@@ -2913,7 +4621,7 @@
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="J5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K5" s="7"/>
     </row>
@@ -2925,7 +4633,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>15</v>
@@ -2936,7 +4644,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="J6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K6" s="8"/>
     </row>
@@ -2945,10 +4653,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>
@@ -3007,7 +4715,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>42</v>
@@ -3061,10 +4769,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>55</v>
@@ -3083,7 +4791,7 @@
         <v>57</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>55</v>
@@ -3102,7 +4810,7 @@
         <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>15</v>
@@ -3114,7 +4822,7 @@
         <v>400000000</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H15" s="7"/>
     </row>
@@ -3126,10 +4834,10 @@
         <v>76</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>11</v>
@@ -3138,7 +4846,7 @@
         <v>5000000</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H16" s="7"/>
     </row>
@@ -3150,10 +4858,10 @@
         <v>79</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>11</v>
@@ -3167,16 +4875,16 @@
         <v>72</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -3186,54 +4894,54 @@
         <v>75</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>86</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
     </row>
     <row r="20" ht="45" spans="1:8">
       <c r="A20" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
     </row>
     <row r="21" ht="30" spans="1:8">
       <c r="A21" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
@@ -3243,16 +4951,16 @@
         <v>83</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -3262,16 +4970,16 @@
         <v>87</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
@@ -3296,16 +5004,16 @@
         <v>150000000</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>65</v>
@@ -3327,13 +5035,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>11</v>
@@ -3353,7 +5061,7 @@
         <v>69</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>11</v>
@@ -3370,13 +5078,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>11</v>
@@ -3389,13 +5097,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>101</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>11</v>
@@ -3408,10 +5116,10 @@
         <v>115</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>15</v>
@@ -3427,13 +5135,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>11</v>
@@ -3490,7 +5198,7 @@
         <v>117</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>11</v>
@@ -3519,7 +5227,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>123</v>
@@ -3528,7 +5236,7 @@
         <v>123</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>125</v>
@@ -3538,16 +5246,16 @@
     </row>
     <row r="37" ht="45" spans="1:7">
       <c r="A37" s="5" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>127</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>11</v>
@@ -3557,7 +5265,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>131</v>
@@ -3566,7 +5274,7 @@
         <v>132</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>11</v>
@@ -3576,7 +5284,7 @@
     </row>
     <row r="39" ht="30" spans="1:7">
       <c r="A39" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>135</v>
@@ -3585,7 +5293,7 @@
         <v>136</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>11</v>

--- a/MSME/MSME intrim claim calculations.xlsx
+++ b/MSME/MSME intrim claim calculations.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Intrim claim(OTS=N)" sheetId="3" r:id="rId1"/>
     <sheet name="Intrim claim (OTS=Y)" sheetId="5" r:id="rId2"/>
     <sheet name="Final claim(OTS=N)" sheetId="2" r:id="rId3"/>
     <sheet name="Final claim(OTS=Y)" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="220">
   <si>
     <t>S. No.</t>
   </si>
@@ -698,6 +699,9 @@
     <t>Auto-calculation. 2*(28+29)</t>
   </si>
   <si>
+    <t>Auto-calculate</t>
+  </si>
+  <si>
     <t>32</t>
   </si>
   <si>
@@ -723,6 +727,309 @@
   </si>
   <si>
     <t>Auto-calc. If 27=33 then 0 else 27-33</t>
+  </si>
+  <si>
+    <t>sr no</t>
+  </si>
+  <si>
+    <t>Feedback / Requirement</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <r>
+      <t>NCGTC Accountant – Payment:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Show </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Amount Available for Payment Against Current Claim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> instead of </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Interim Claim Calculated &amp; Payable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <r>
+      <t>NCGTC Creator/Approver:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Display all claim lodgement records along with an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MLI Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> filter.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Audit Trail:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Display only the role instead of the NCGTC user name and include the Accountant role in the audit trail.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>On Hold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Facing an implementation issue.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Recovery:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Auto-populate the Recovery Amount from NPA date until Final Claim, with the option to edit the amount.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Recovery:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Allow recovery only for cases where the Interim Claim has been settled; otherwise, display an appropriate error.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Recovery Report:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Report logic to be based on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Payment Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Claim Report:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Report logic to be based on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Claim Payout Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NPA Report:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Logic to be based on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NPA Marking Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> instead of the NPA Date.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MLI-wise Claim Payout Capping Report:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Development as per the calculation Excel shared earlier by the client.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – As discussed, this needs to be developed as a dashboard.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -735,7 +1042,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,8 +1222,16 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -944,12 +1259,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1299,7 +1608,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1323,16 +1632,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1341,92 +1650,104 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1463,7 +1784,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1475,9 +1799,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1487,10 +1808,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2027,534 +2348,534 @@
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="14" customWidth="1"/>
-    <col min="2" max="2" width="38" style="14" customWidth="1"/>
-    <col min="3" max="3" width="64" style="14" customWidth="1"/>
-    <col min="4" max="4" width="48.2857142857143" style="14" customWidth="1"/>
-    <col min="5" max="5" width="34.2857142857143" style="14" customWidth="1"/>
-    <col min="6" max="6" width="21.2857142857143" style="15" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="15" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="19" customWidth="1"/>
+    <col min="2" max="2" width="38" style="19" customWidth="1"/>
+    <col min="3" max="3" width="64" style="19" customWidth="1"/>
+    <col min="4" max="4" width="48.2857142857143" style="19" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="20" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="20" customWidth="1"/>
     <col min="8" max="9" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="E2" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" ht="30" spans="1:8">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
+      <c r="E3" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
+      <c r="E4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="E5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" ht="30" spans="1:8">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
+      <c r="E6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" ht="30" spans="1:8">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="E7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="E8" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:8">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
     </row>
     <row r="11" ht="30" spans="1:8">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" ht="30" spans="1:8">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
     </row>
     <row r="13" ht="30" spans="1:8">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" ht="30" spans="1:8">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="E15" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="23">
         <v>50000000</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="22"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="E16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="14">
         <v>60000000</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="22"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="19">
+      <c r="E17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="23">
         <f>MAX(F15,F16)</f>
         <v>60000000</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="26"/>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="19">
+      <c r="E18" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="23">
         <v>100000000</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="22"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="19">
+      <c r="E19" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="23">
         <v>100000000</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="22"/>
+      <c r="H19" s="26"/>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="14">
         <v>0</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="22"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="19">
+      <c r="E21" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="23">
         <f>F18</f>
         <v>100000000</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="8"/>
+      <c r="H21" s="12"/>
     </row>
     <row r="22" ht="30" spans="1:10">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="19">
+      <c r="E22" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="23">
         <f>F19</f>
         <v>100000000</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="8"/>
+      <c r="H22" s="12"/>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="23">
         <f>F20</f>
         <v>0</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="12"/>
     </row>
     <row r="24" ht="120" spans="1:10">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="19">
+      <c r="E24" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="23">
         <f>IF(F8="N",F18+F19-F20,IF(F8="Y",F18+F19-F13,""))</f>
         <v>200000000</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="23"/>
+      <c r="H24" s="27"/>
       <c r="I24">
         <f>IF(F8="N",F21+F22-F23,IF(F8="Y",F21+F22-F13,""))</f>
         <v>200000000</v>
@@ -2564,249 +2885,249 @@
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="19">
+      <c r="E25" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="23">
         <f>60%*(F24-F17)</f>
         <v>84000000</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="23"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="19">
+      <c r="E26" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="23">
         <f>IF(F8="N",75%*F25,IF(F8="Y",100%*F25,""))</f>
         <v>63000000</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="23"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="19">
+      <c r="E27" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="23">
         <v>5487293.76</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="23"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" ht="45" spans="1:10">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="19">
+      <c r="E28" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="23">
         <v>0</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="23"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="E29" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="23">
         <f>2*(F27+F28)</f>
         <v>10974587.52</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="23"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="10">
+      <c r="E30" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="14">
         <v>0</v>
       </c>
-      <c r="G30" s="19"/>
-      <c r="H30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="23">
         <f>F29-F30</f>
         <v>10974587.52</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="23"/>
+      <c r="H31" s="27"/>
     </row>
     <row r="32" ht="60" spans="1:10">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="19">
+      <c r="E32" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="23">
         <f>IF(F26&lt;=F31,F26,F31)</f>
         <v>10974587.52</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="23"/>
+      <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="19">
+      <c r="E33" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="23">
         <f>F31-F32</f>
         <v>0</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="23"/>
+      <c r="H33" s="27"/>
     </row>
     <row r="34" ht="30" spans="1:8">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="19">
+      <c r="E34" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="23">
         <f>IF(F32&lt;F26,F26-F32)</f>
         <v>52025412.48</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="23"/>
+      <c r="H34" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2820,259 +3141,259 @@
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.4190476190476" style="13" customWidth="1"/>
-    <col min="2" max="2" width="38" style="14" customWidth="1"/>
-    <col min="3" max="3" width="64" style="14" customWidth="1"/>
-    <col min="4" max="4" width="39.6571428571429" style="14" customWidth="1"/>
-    <col min="5" max="5" width="34.2857142857143" style="14" customWidth="1"/>
-    <col min="6" max="6" width="21.2857142857143" style="15" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="15" customWidth="1"/>
+    <col min="1" max="1" width="10.4190476190476" style="18" customWidth="1"/>
+    <col min="2" max="2" width="38" style="19" customWidth="1"/>
+    <col min="3" max="3" width="64" style="19" customWidth="1"/>
+    <col min="4" max="4" width="39.6571428571429" style="19" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="20" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="20" customWidth="1"/>
     <col min="8" max="8" width="9.4" customWidth="1"/>
-    <col min="9" max="9" width="21.2857142857143" style="15" customWidth="1"/>
+    <col min="9" max="9" width="21.2857142857143" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="E2" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" ht="30" spans="1:10">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="E3" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="E4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="E5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" ht="30" spans="1:10">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="E6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" ht="30" spans="1:10">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="E7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="E8" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="19" t="str">
+      <c r="I8" s="23" t="str">
         <f>F8</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:10">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19" t="s">
+      <c r="F9" s="23"/>
+      <c r="G9" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="19"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="23">
         <v>10000</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="I10" s="19">
+      <c r="G10" s="23"/>
+      <c r="I10" s="23">
         <f>F10</f>
         <v>10000</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="23">
         <f>F10</f>
         <v>10000</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="I11" s="19">
+      <c r="G11" s="23"/>
+      <c r="I11" s="23">
         <f>F11</f>
         <v>10000</v>
       </c>
@@ -3081,248 +3402,248 @@
       </c>
     </row>
     <row r="12" ht="30" spans="1:10">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="23">
         <v>2000</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="I12" s="19">
+      <c r="G12" s="23"/>
+      <c r="I12" s="23">
         <f>F12</f>
         <v>2000</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:10">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="23">
         <f>40%*(F10-F12)</f>
         <v>3200</v>
       </c>
-      <c r="G13" s="19"/>
-      <c r="I13" s="19">
+      <c r="G13" s="23"/>
+      <c r="I13" s="23">
         <f>40%*(I11-I12)</f>
         <v>3200</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:10">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="23">
         <f>60%*(F10-F12)</f>
         <v>4800</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="I14" s="19">
+      <c r="G14" s="23"/>
+      <c r="I14" s="23">
         <f>60%*(I10-I12)</f>
         <v>4800</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="E15" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="23">
         <v>50000000</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="22"/>
-      <c r="I15" s="19">
+      <c r="H15" s="26"/>
+      <c r="I15" s="23">
         <f>F15</f>
         <v>50000000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="E16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="14">
         <v>60000000</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="10">
+      <c r="H16" s="26"/>
+      <c r="I16" s="14">
         <f>F16</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="19">
+      <c r="E17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="23">
         <f>MAX(F15,F16)</f>
         <v>60000000</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="22"/>
-      <c r="I17" s="19">
+      <c r="H17" s="26"/>
+      <c r="I17" s="23">
         <f>MAX(I15,I16)</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="19">
+      <c r="E18" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="23">
         <v>200000000</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="19">
+      <c r="H18" s="26"/>
+      <c r="I18" s="23">
         <f>F18</f>
         <v>200000000</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="19">
+      <c r="E19" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="23">
         <v>200000000</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="22"/>
-      <c r="I19" s="19">
+      <c r="H19" s="26"/>
+      <c r="I19" s="23">
         <f>F19</f>
         <v>200000000</v>
       </c>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="19">
+      <c r="E20" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="23">
         <f>F18</f>
         <v>200000000</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="19">
+      <c r="H20" s="12"/>
+      <c r="I20" s="23">
         <f>F20</f>
         <v>200000000</v>
       </c>
@@ -3331,30 +3652,30 @@
       </c>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="19">
+      <c r="E21" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="23">
         <f>F19</f>
         <v>200000000</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="19">
+      <c r="H21" s="12"/>
+      <c r="I21" s="23">
         <f>F21</f>
         <v>200000000</v>
       </c>
@@ -3363,309 +3684,309 @@
       </c>
     </row>
     <row r="22" ht="120" spans="1:10">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="19">
+      <c r="E22" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="23">
         <f>IF(F8="N",F18+F19-#REF!,IF(F8="Y",F18+F19-F13,""))</f>
         <v>399996800</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="23"/>
-      <c r="I22" s="19">
+      <c r="H22" s="27"/>
+      <c r="I22" s="23">
         <f>IF(I8="N",I18+I19-#REF!,IF(I8="Y",I18+I19-I13,""))</f>
         <v>399996800</v>
       </c>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="19">
+      <c r="E23" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="23">
         <f>60%*(F22-F17)</f>
         <v>203998080</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="23"/>
-      <c r="I23" s="19">
+      <c r="H23" s="27"/>
+      <c r="I23" s="23">
         <f>60%*(I22-I17)</f>
         <v>203998080</v>
       </c>
     </row>
     <row r="24" ht="45" spans="1:10">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="19">
+      <c r="E24" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="23">
         <f>IF(F8="N",75%*F23,IF(F8="Y",100%*F23,""))</f>
         <v>203998080</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="23"/>
-      <c r="I24" s="19">
+      <c r="H24" s="27"/>
+      <c r="I24" s="23">
         <f>IF(I8="N",75%*I23,IF(I8="Y",100%*I23,""))</f>
         <v>203998080</v>
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="19">
+      <c r="E25" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="23">
         <v>0</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H25" s="23"/>
-      <c r="I25" s="19">
+      <c r="H25" s="27"/>
+      <c r="I25" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="19">
+      <c r="E26" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="23">
         <v>0</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H26" s="23"/>
-      <c r="I26" s="19">
+      <c r="H26" s="27"/>
+      <c r="I26" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:10">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="19">
+      <c r="E27" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="23">
         <f>2*(F25+F26)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H27" s="23"/>
-      <c r="I27" s="19">
+      <c r="H27" s="27"/>
+      <c r="I27" s="23">
         <f>2*(I25+I26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:10">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="10">
+      <c r="E28" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="14">
         <v>0</v>
       </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="10">
+      <c r="G28" s="23"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="23">
         <f>F27-F28</f>
         <v>0</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="19">
+      <c r="H29" s="27"/>
+      <c r="I29" s="23">
         <f>I27-I28</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="60" spans="1:10">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="19">
+      <c r="E30" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="23">
         <f>IF(F24&lt;=F29,F24,F29)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="23"/>
-      <c r="I30" s="19">
+      <c r="H30" s="27"/>
+      <c r="I30" s="23">
         <f>IF(I24&lt;=I29,I24,I29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="19">
+      <c r="E31" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="23">
         <f>F29-F30</f>
         <v>0</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="23"/>
-      <c r="I31" s="19">
+      <c r="H31" s="27"/>
+      <c r="I31" s="23">
         <f>I29-I30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:10">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19" t="s">
+      <c r="E32" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="19"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3679,408 +4000,424 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="49.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="42.2857142857143" style="1" customWidth="1"/>
-    <col min="5" max="5" width="31.4285714285714" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.2857142857143" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.8571428571429" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.57142857142857"/>
+    <col min="1" max="1" width="6.71428571428571" style="5" customWidth="1"/>
+    <col min="2" max="2" width="42.5714285714286" style="5" customWidth="1"/>
+    <col min="3" max="3" width="49.1428571428571" style="5" customWidth="1"/>
+    <col min="4" max="4" width="42.2857142857143" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31.4285714285714" style="5" customWidth="1"/>
+    <col min="6" max="6" width="27.2857142857143" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.8571428571429" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.8571428571429"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="E2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="E3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="E4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
       <c r="J5" t="s">
         <v>144</v>
       </c>
-      <c r="K5" s="7"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" ht="75" spans="1:11">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="E6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
       <c r="J6" t="s">
         <v>146</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" ht="45" spans="1:11">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
+      <c r="E8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9" ht="30" spans="1:11">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" ht="45" spans="1:11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" ht="45" spans="1:11">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="30" spans="1:11">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" ht="60" spans="1:11">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="E15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10">
         <v>100000000</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="11"/>
+      <c r="I15">
+        <f>F15</f>
+        <v>100000000</v>
+      </c>
     </row>
     <row r="16" ht="45" spans="1:11">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="E16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="10">
         <v>100000000</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="11"/>
+      <c r="I16">
+        <f>F16</f>
+        <v>100000000</v>
+      </c>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="E17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="10">
         <v>10</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
+      <c r="I17">
+        <f>F17</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="18" ht="45" spans="1:10">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="10">
         <v>80000000</v>
       </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" ht="45" spans="1:10">
-      <c r="A19" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F19" s="6">
+      <c r="G18" s="10"/>
+      <c r="I18">
         <f>F18</f>
         <v>80000000</v>
       </c>
-      <c r="G19" s="6"/>
+    </row>
+    <row r="19" ht="45" spans="1:10">
+      <c r="A19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="10">
+        <f>F18</f>
+        <v>80000000</v>
+      </c>
+      <c r="G19" s="10"/>
       <c r="I19">
         <f>F19</f>
         <v>80000000</v>
@@ -4090,416 +4427,510 @@
       </c>
     </row>
     <row r="20" ht="45" spans="1:10">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="10">
         <f>40%*F18</f>
         <v>32000000</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="10"/>
       <c r="I20">
         <f>40%*I19</f>
         <v>32000000</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="10">
         <f>60%*F18</f>
         <v>48000000</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="10"/>
       <c r="I21">
         <f>60%*I19</f>
         <v>48000000</v>
       </c>
     </row>
     <row r="22" ht="60" spans="1:10">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="E24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="10">
         <v>50000000</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="11"/>
+      <c r="I24">
+        <f>F24</f>
+        <v>50000000</v>
+      </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="5">
+      <c r="E25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="9">
         <v>60000000</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11"/>
+      <c r="I25">
+        <f>F25</f>
+        <v>60000000</v>
+      </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="E26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="10">
         <v>1</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="7"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
     </row>
     <row r="27" ht="30" spans="1:10">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="E27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="10">
         <f>MAX(F24,F25)</f>
         <v>60000000</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+      <c r="I27">
+        <f>F27</f>
+        <v>60000000</v>
+      </c>
     </row>
     <row r="28" ht="120" spans="1:10">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="6">
+      <c r="E28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="10">
         <f>F15+F16-F17-F20</f>
         <v>167999990</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="10"/>
+      <c r="I28">
+        <f>I15+I16-I17-I20</f>
+        <v>167999990</v>
+      </c>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
+      <c r="E29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="10">
+        <f>60%*(F28-F27)</f>
+        <v>64799994</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="I29">
+        <f>60%*(I28-I27)</f>
+        <v>64799994</v>
+      </c>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+      <c r="E30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="17">
+        <v>62999995.5</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30">
+        <f>F30</f>
+        <v>62999995.5</v>
+      </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="E31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="10">
+        <f>F29-F30</f>
+        <v>1799998.5</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="I31">
+        <f>F31</f>
+        <v>1799998.5</v>
+      </c>
     </row>
     <row r="32" ht="30" spans="1:10">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" ht="30" spans="1:7">
-      <c r="A33" s="5" t="s">
+      <c r="E32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="10">
+        <v>5487293.76</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I32">
+        <f>F32</f>
+        <v>5487293.76</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="1:9">
+      <c r="A33" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" ht="30" spans="1:7">
-      <c r="A34" s="5" t="s">
+      <c r="E33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="10">
+        <v>0</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I33">
+        <f>F33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="30" spans="1:9">
+      <c r="A34" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="5" t="s">
+      <c r="E34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="10">
+        <f>2*(F33+F32)</f>
+        <v>10974587.52</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="I34">
+        <f>F34</f>
+        <v>10974587.52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="5" t="s">
+      <c r="E35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I35">
+        <f>F35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="10">
+        <f>F34-F35</f>
+        <v>10974587.52</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" ht="45" spans="1:7">
-      <c r="A37" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="I36">
+        <f>I34-I35</f>
+        <v>10974587.52</v>
+      </c>
+    </row>
+    <row r="37" ht="45" spans="1:9">
+      <c r="A37" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="5" t="s">
+      <c r="D37" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="E37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="10">
+        <f>IF(F31&lt;=F36,F31,F36)</f>
+        <v>1799998.5</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="I37" s="10">
+        <f>IF(I31&lt;=I36,I31,I36)</f>
+        <v>1799998.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" ht="30" spans="1:7">
-      <c r="A39" s="5" t="s">
+      <c r="D38" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="E38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="10">
+        <f>F36-F37</f>
+        <v>9174589.02</v>
+      </c>
+      <c r="G38" s="10"/>
+      <c r="I38" s="10">
+        <f>I36-I37</f>
+        <v>9174589.02</v>
+      </c>
+    </row>
+    <row r="39" ht="30" spans="1:9">
+      <c r="A39" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="D39" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4513,793 +4944,919 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="49.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="42.2857142857143" style="1" customWidth="1"/>
-    <col min="5" max="5" width="31.4285714285714" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.2857142857143" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.8571428571429" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="5" customWidth="1"/>
+    <col min="2" max="2" width="42.5714285714286" style="5" customWidth="1"/>
+    <col min="3" max="3" width="49.1428571428571" style="5" customWidth="1"/>
+    <col min="4" max="4" width="42.2857142857143" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31.4285714285714" style="5" customWidth="1"/>
+    <col min="6" max="6" width="27.2857142857143" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.8571428571429" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="E2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" ht="30" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="E3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="E4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
       <c r="J5" t="s">
         <v>144</v>
       </c>
-      <c r="K5" s="7"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" ht="75" spans="1:11">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="E6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
       <c r="J6" t="s">
         <v>146</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" ht="45" spans="1:11">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
+      <c r="E8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9" ht="30" spans="1:11">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" ht="45" spans="1:11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" ht="45" spans="1:11">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="30" spans="1:11">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" ht="60" spans="1:11">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="E15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10">
         <v>400000000</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16" ht="45" spans="1:11">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="E16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="10">
         <v>5000000</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="17" ht="30" spans="1:8">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
+      <c r="E17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" ht="45" spans="1:8">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" ht="45" spans="1:8">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" ht="45" spans="1:8">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" ht="30" spans="1:8">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" ht="60" spans="1:8">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="E24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="10">
         <v>150000000</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="6">
+      <c r="E25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="10">
         <v>150000001</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="7"/>
+      <c r="E26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
     </row>
     <row r="27" ht="30" spans="1:8">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="E27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="10">
         <f>MAX(F24,F25)</f>
         <v>150000001</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
     </row>
     <row r="28" ht="120" spans="1:8">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+      <c r="E28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
     </row>
     <row r="29" ht="30" spans="1:8">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
+      <c r="E29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" ht="30" spans="1:8">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+      <c r="E30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="E31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" ht="30" spans="1:8">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="E32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" ht="30" spans="1:7">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="E33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" ht="30" spans="1:7">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="E34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="E35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="D36" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
     </row>
     <row r="37" ht="45" spans="1:7">
-      <c r="A37" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="A37" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
+      <c r="D37" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
+      <c r="D38" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
     </row>
     <row r="39" ht="30" spans="1:7">
-      <c r="A39" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="A39" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="D39" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="82.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="40.1428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="1:3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>219</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MSME/MSME intrim claim calculations.xlsx
+++ b/MSME/MSME intrim claim calculations.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="4"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Intrim claim(OTS=N)" sheetId="3" r:id="rId1"/>
@@ -739,6 +739,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>NCGTC Accountant – Payment:</t>
     </r>
     <r>
@@ -799,6 +807,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>NCGTC Creator/Approver:</t>
     </r>
     <r>
@@ -835,6 +851,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Audit Trail:</t>
     </r>
     <r>
@@ -850,6 +874,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>On Hold</t>
     </r>
     <r>
@@ -865,6 +897,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Recovery:</t>
     </r>
     <r>
@@ -880,6 +920,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Recovery:</t>
     </r>
     <r>
@@ -895,6 +943,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Recovery Report:</t>
     </r>
     <r>
@@ -931,6 +987,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Claim Report:</t>
     </r>
     <r>
@@ -967,6 +1031,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>NPA Report:</t>
     </r>
     <r>
@@ -1003,6 +1075,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>MLI-wise Claim Payout Capping Report:</t>
     </r>
     <r>
@@ -1018,6 +1098,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Pending</t>
     </r>
     <r>
@@ -1036,11 +1124,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1732,7 +1821,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1793,15 +1882,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1813,6 +1911,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -2353,25 +2454,25 @@
     <col min="3" max="3" width="64" style="19" customWidth="1"/>
     <col min="4" max="4" width="48.2857142857143" style="19" customWidth="1"/>
     <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
-    <col min="6" max="6" width="21.2857142857143" style="20" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="20" customWidth="1"/>
+    <col min="6" max="6" width="21.2857142857143" style="21" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
     <col min="8" max="9" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -2382,500 +2483,500 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
+      <c r="E2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" ht="30" spans="1:8">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
+      <c r="E3" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="E4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
+      <c r="E5" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" ht="30" spans="1:8">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="E6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" ht="30" spans="1:8">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
+      <c r="E7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="26" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:8">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" ht="30" spans="1:8">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" ht="30" spans="1:8">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" ht="30" spans="1:8">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" ht="30" spans="1:8">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="23">
+      <c r="E15" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="26">
         <v>50000000</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="26"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="14">
         <v>60000000</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="26"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="23">
+      <c r="E17" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="26">
         <f>MAX(F15,F16)</f>
         <v>60000000</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="26"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="23">
+      <c r="E18" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="26">
         <v>100000000</v>
       </c>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="26"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="23">
+      <c r="E19" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="26">
         <v>100000000</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="26"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="24" t="s">
         <v>82</v>
       </c>
       <c r="F20" s="14">
         <v>0</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="26"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="23">
+      <c r="E21" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="26">
         <f>F18</f>
         <v>100000000</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H21" s="12"/>
     </row>
     <row r="22" ht="30" spans="1:10">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="23">
+      <c r="E22" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="26">
         <f>F19</f>
         <v>100000000</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H22" s="12"/>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="26">
         <f>F20</f>
         <v>0</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H23" s="12"/>
     </row>
     <row r="24" ht="120" spans="1:10">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="23">
+      <c r="E24" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="26">
         <f>IF(F8="N",F18+F19-F20,IF(F8="Y",F18+F19-F13,""))</f>
         <v>200000000</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="27"/>
+      <c r="H24" s="31"/>
       <c r="I24">
         <f>IF(F8="N",F21+F22-F23,IF(F8="Y",F21+F22-F13,""))</f>
         <v>200000000</v>
@@ -2885,249 +2986,249 @@
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="23">
+      <c r="E25" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="26">
         <f>60%*(F24-F17)</f>
         <v>84000000</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="27"/>
+      <c r="H25" s="31"/>
     </row>
     <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="23">
+      <c r="E26" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="26">
         <f>IF(F8="N",75%*F25,IF(F8="Y",100%*F25,""))</f>
         <v>63000000</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="27"/>
+      <c r="H26" s="31"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="23">
+      <c r="E27" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="26">
         <v>5487293.76</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="27"/>
+      <c r="H27" s="31"/>
     </row>
     <row r="28" ht="45" spans="1:10">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="23">
+      <c r="E28" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="26">
         <v>0</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="27"/>
+      <c r="H28" s="31"/>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="23">
+      <c r="E29" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="26">
         <f>2*(F27+F28)</f>
         <v>10974587.52</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="27"/>
+      <c r="H29" s="31"/>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="14">
         <v>0</v>
       </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="27"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="31"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="26">
         <f>F29-F30</f>
         <v>10974587.52</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="27"/>
+      <c r="H31" s="31"/>
     </row>
     <row r="32" ht="60" spans="1:10">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="23">
+      <c r="E32" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="26">
         <f>IF(F26&lt;=F31,F26,F31)</f>
         <v>10974587.52</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="27"/>
+      <c r="H32" s="31"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="23">
+      <c r="E33" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="26">
         <f>F31-F32</f>
         <v>0</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="G33" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="27"/>
+      <c r="H33" s="31"/>
     </row>
     <row r="34" ht="30" spans="1:8">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="23">
+      <c r="E34" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="26">
         <f>IF(F32&lt;F26,F26-F32)</f>
         <v>52025412.48</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="27"/>
+      <c r="H34" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3147,28 +3248,28 @@
     <col min="4" max="4" width="39.6571428571429" style="19" customWidth="1"/>
     <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
     <col min="6" max="6" width="21.2857142857143" style="20" customWidth="1"/>
-    <col min="7" max="7" width="16.5714285714286" style="20" customWidth="1"/>
+    <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
     <col min="8" max="8" width="9.4" customWidth="1"/>
-    <col min="9" max="9" width="21.2857142857143" style="20" customWidth="1"/>
+    <col min="9" max="9" width="21.2857142857143" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="23" t="s">
         <v>138</v>
       </c>
       <c r="G1" s="7" t="s">
@@ -3179,814 +3280,811 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="I2" s="23"/>
+      <c r="E2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" ht="30" spans="1:10">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="E3" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="25"/>
+      <c r="G3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="I4" s="23"/>
+      <c r="E4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="25"/>
+      <c r="G4" s="26"/>
+      <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="I5" s="23"/>
+      <c r="E5" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="G5" s="26"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" ht="30" spans="1:10">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="I6" s="23"/>
+      <c r="E6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="25"/>
+      <c r="G6" s="26"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" ht="30" spans="1:10">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="I7" s="23"/>
+      <c r="E7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="23" t="str">
+      <c r="I8" s="26" t="str">
         <f>F8</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:10">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23" t="s">
+      <c r="F9" s="25"/>
+      <c r="G9" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="23"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="23">
-        <v>10000</v>
-      </c>
-      <c r="G10" s="23"/>
-      <c r="I10" s="23">
+      <c r="F10" s="25">
+        <v>100010008</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="I10" s="26">
         <f>F10</f>
-        <v>10000</v>
+        <v>100010008</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="25">
         <f>F10</f>
-        <v>10000</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="I11" s="23">
-        <f>F11</f>
-        <v>10000</v>
+        <v>100010008</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="I11" s="26">
+        <v>345452343</v>
       </c>
       <c r="J11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:10">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="23">
-        <v>2000</v>
-      </c>
-      <c r="G12" s="23"/>
-      <c r="I12" s="23">
+      <c r="F12" s="25">
+        <v>1000000</v>
+      </c>
+      <c r="G12" s="26"/>
+      <c r="I12" s="26">
         <f>F12</f>
-        <v>2000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:10">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="25">
         <f>40%*(F10-F12)</f>
-        <v>3200</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="I13" s="23">
+        <v>39604003.2</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="I13" s="26">
         <f>40%*(I11-I12)</f>
-        <v>3200</v>
+        <v>137780937.2</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:10">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="25">
         <f>60%*(F10-F12)</f>
-        <v>4800</v>
-      </c>
-      <c r="G14" s="23"/>
-      <c r="I14" s="23">
+        <v>59406004.8</v>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="I14" s="26">
         <f>60%*(I10-I12)</f>
-        <v>4800</v>
+        <v>59406004.8</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="23">
+      <c r="E15" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="25">
         <v>50000000</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="23">
+      <c r="H15" s="29"/>
+      <c r="I15" s="26">
         <f>F15</f>
         <v>50000000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="E16" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="30">
         <v>60000000</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="26"/>
+      <c r="H16" s="29"/>
       <c r="I16" s="14">
         <f>F16</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="23">
+      <c r="E17" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="25">
         <f>MAX(F15,F16)</f>
         <v>60000000</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="26"/>
-      <c r="I17" s="23">
+      <c r="H17" s="29"/>
+      <c r="I17" s="26">
         <f>MAX(I15,I16)</f>
         <v>60000000</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="23">
-        <v>200000000</v>
-      </c>
-      <c r="G18" s="23" t="s">
+      <c r="E18" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="25">
+        <v>300000000</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="23">
+      <c r="H18" s="29"/>
+      <c r="I18" s="26">
         <f>F18</f>
-        <v>200000000</v>
+        <v>300000000</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="23">
-        <v>200000000</v>
-      </c>
-      <c r="G19" s="23" t="s">
+      <c r="E19" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="25">
+        <v>100</v>
+      </c>
+      <c r="G19" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="23">
+      <c r="H19" s="29"/>
+      <c r="I19" s="26">
         <f>F19</f>
-        <v>200000000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="23">
+      <c r="E20" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="25">
         <f>F18</f>
-        <v>200000000</v>
-      </c>
-      <c r="G20" s="23" t="s">
+        <v>300000000</v>
+      </c>
+      <c r="G20" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H20" s="12"/>
-      <c r="I20" s="23">
-        <f>F20</f>
-        <v>200000000</v>
+      <c r="I20" s="26">
+        <v>300450000</v>
       </c>
       <c r="J20" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="23">
+      <c r="E21" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="25">
         <f>F19</f>
-        <v>200000000</v>
-      </c>
-      <c r="G21" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H21" s="12"/>
-      <c r="I21" s="23">
-        <f>F21</f>
-        <v>200000000</v>
+      <c r="I21" s="26">
+        <v>1000</v>
       </c>
       <c r="J21" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="22" ht="120" spans="1:10">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="23">
+      <c r="E22" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="25">
         <f>IF(F8="N",F18+F19-#REF!,IF(F8="Y",F18+F19-F13,""))</f>
-        <v>399996800</v>
-      </c>
-      <c r="G22" s="23" t="s">
+        <v>260396096.8</v>
+      </c>
+      <c r="G22" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="27"/>
-      <c r="I22" s="23">
+      <c r="H22" s="31"/>
+      <c r="I22" s="26">
         <f>IF(I8="N",I18+I19-#REF!,IF(I8="Y",I18+I19-I13,""))</f>
-        <v>399996800</v>
+        <v>162219162.8</v>
       </c>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="23">
+      <c r="E23" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="25">
         <f>60%*(F22-F17)</f>
-        <v>203998080</v>
-      </c>
-      <c r="G23" s="23" t="s">
+        <v>120237658.08</v>
+      </c>
+      <c r="G23" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="27"/>
-      <c r="I23" s="23">
+      <c r="H23" s="31"/>
+      <c r="I23" s="26">
         <f>60%*(I22-I17)</f>
-        <v>203998080</v>
+        <v>61331497.68</v>
       </c>
     </row>
     <row r="24" ht="45" spans="1:10">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="23">
+      <c r="E24" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="25">
         <f>IF(F8="N",75%*F23,IF(F8="Y",100%*F23,""))</f>
-        <v>203998080</v>
-      </c>
-      <c r="G24" s="23" t="s">
+        <v>120237658.08</v>
+      </c>
+      <c r="G24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="27"/>
-      <c r="I24" s="23">
+      <c r="H24" s="31"/>
+      <c r="I24" s="26">
         <f>IF(I8="N",75%*I23,IF(I8="Y",100%*I23,""))</f>
-        <v>203998080</v>
+        <v>61331497.68</v>
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="23">
+      <c r="E25" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="25">
+        <v>142919013.51</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="31"/>
+      <c r="I25" s="26">
         <v>0</v>
       </c>
-      <c r="G25" s="23" t="s">
+    </row>
+    <row r="26" ht="45" spans="1:10">
+      <c r="A26" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="25">
+        <v>0</v>
+      </c>
+      <c r="G26" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H25" s="27"/>
-      <c r="I25" s="23">
+      <c r="H26" s="31"/>
+      <c r="I26" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="23">
-        <v>0</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26" s="27"/>
-      <c r="I26" s="23">
-        <v>0</v>
-      </c>
-    </row>
     <row r="27" ht="30" spans="1:10">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="23">
+      <c r="E27" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="25">
         <f>2*(F25+F26)</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="23" t="s">
+        <v>285838027.02</v>
+      </c>
+      <c r="G27" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="23">
+      <c r="H27" s="31"/>
+      <c r="I27" s="26">
         <f>2*(I25+I26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:10">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="E28" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="30">
         <v>0</v>
       </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="27"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="31"/>
       <c r="I28" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="25">
         <f>F27-F28</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="23" t="s">
+        <v>285838027.02</v>
+      </c>
+      <c r="G29" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="27"/>
-      <c r="I29" s="23">
+      <c r="H29" s="31"/>
+      <c r="I29" s="26">
         <f>I27-I28</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="60" spans="1:10">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="23">
+      <c r="E30" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="25">
         <f>IF(F24&lt;=F29,F24,F29)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="23" t="s">
+        <v>120237658.08</v>
+      </c>
+      <c r="G30" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="27"/>
-      <c r="I30" s="23">
+      <c r="H30" s="31"/>
+      <c r="I30" s="26">
         <f>IF(I24&lt;=I29,I24,I29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="23">
+      <c r="E31" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="25">
         <f>F29-F30</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="23" t="s">
+        <v>165600368.94</v>
+      </c>
+      <c r="G31" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="27"/>
-      <c r="I31" s="23">
+      <c r="H31" s="31"/>
+      <c r="I31" s="26">
         <f>I29-I30</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:10">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23" t="s">
+      <c r="E32" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="25"/>
+      <c r="G32" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="27"/>
-      <c r="I32" s="23"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4694,7 +4792,7 @@
         <v>178</v>
       </c>
       <c r="I30">
-        <f>F30</f>
+        <f t="shared" ref="I30:I35" si="0">F30</f>
         <v>62999995.5</v>
       </c>
     </row>
@@ -4720,7 +4818,7 @@
       </c>
       <c r="G31" s="10"/>
       <c r="I31">
-        <f>F31</f>
+        <f t="shared" si="0"/>
         <v>1799998.5</v>
       </c>
     </row>
@@ -4747,7 +4845,7 @@
         <v>178</v>
       </c>
       <c r="I32">
-        <f>F32</f>
+        <f t="shared" si="0"/>
         <v>5487293.76</v>
       </c>
     </row>
@@ -4774,7 +4872,7 @@
         <v>178</v>
       </c>
       <c r="I33">
-        <f>F33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -4802,7 +4900,7 @@
         <v>195</v>
       </c>
       <c r="I34">
-        <f>F34</f>
+        <f t="shared" si="0"/>
         <v>10974587.52</v>
       </c>
     </row>
@@ -4829,7 +4927,7 @@
         <v>178</v>
       </c>
       <c r="I35">
-        <f>F35</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/MSME/MSME intrim claim calculations.xlsx
+++ b/MSME/MSME intrim claim calculations.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="225">
   <si>
     <t>S. No.</t>
   </si>
@@ -528,6 +528,47 @@
   </si>
   <si>
     <t>Ediatble</t>
+  </si>
+  <si>
+    <t>MSMETyep</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Amount recovered through OTS ( Proportionate amount of NCGTC recovery ) – 40% of 9A-9C for MLI / 40% of 9B-9C for NCGTC.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NCGTC and MLI portions should be 60% and 40%, respectively, for General MSME, and 75% and 25%, respectively, for Exporter MSME</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Amount recovered through OTS retained by MLI – 60% of 9A-9C for MLI / 60% of 9B-9C for NCGTC.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NCGTC and MLI portions should be 60% and 40%, respectively, for General MSME, and 75% and 25%, respectively, for Exporter MSME</t>
+    </r>
+  </si>
+  <si>
+    <t>Auto Calculate.  75% of AID (21) -Value of collateral (14)</t>
+  </si>
+  <si>
+    <t>Auto-calculation. 3*(24+25)</t>
   </si>
   <si>
     <t>Dropdown Option</t>
@@ -1124,12 +1165,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1821,7 +1863,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1877,32 +1919,62 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1911,9 +1983,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -2449,30 +2518,30 @@
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="19" customWidth="1"/>
-    <col min="2" max="2" width="38" style="19" customWidth="1"/>
-    <col min="3" max="3" width="64" style="19" customWidth="1"/>
-    <col min="4" max="4" width="48.2857142857143" style="19" customWidth="1"/>
-    <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="34" customWidth="1"/>
+    <col min="2" max="2" width="38" style="34" customWidth="1"/>
+    <col min="3" max="3" width="64" style="34" customWidth="1"/>
+    <col min="4" max="4" width="48.2857142857143" style="34" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="34" customWidth="1"/>
     <col min="6" max="6" width="21.2857142857143" style="21" customWidth="1"/>
     <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
     <col min="8" max="9" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -2483,133 +2552,133 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
     </row>
     <row r="3" ht="30" spans="1:8">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
     <row r="6" ht="30" spans="1:8">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
     <row r="7" ht="30" spans="1:8">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="26" t="s">
@@ -2620,133 +2689,133 @@
       </c>
     </row>
     <row r="9" ht="30" spans="1:8">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="38" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
     </row>
     <row r="11" ht="30" spans="1:8">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
     <row r="12" ht="30" spans="1:8">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="38" t="s">
         <v>51</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
     </row>
     <row r="13" ht="30" spans="1:8">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
     </row>
     <row r="14" ht="30" spans="1:8">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="26">
@@ -2755,22 +2824,22 @@
       <c r="G15" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="29"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="14">
@@ -2779,22 +2848,22 @@
       <c r="G16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="29"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="26">
@@ -2804,22 +2873,22 @@
       <c r="G17" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="29"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="26">
@@ -2828,22 +2897,22 @@
       <c r="G18" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="29"/>
+      <c r="H18" s="39"/>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="26">
@@ -2852,22 +2921,22 @@
       <c r="G19" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="29"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="36" t="s">
         <v>82</v>
       </c>
       <c r="F20" s="14">
@@ -2876,22 +2945,22 @@
       <c r="G20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="29"/>
+      <c r="H20" s="39"/>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="26">
@@ -2904,19 +2973,19 @@
       <c r="H21" s="12"/>
     </row>
     <row r="22" ht="30" spans="1:10">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="26">
@@ -2929,19 +2998,19 @@
       <c r="H22" s="12"/>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="36" t="s">
         <v>93</v>
       </c>
       <c r="F23" s="26">
@@ -2954,19 +3023,19 @@
       <c r="H23" s="12"/>
     </row>
     <row r="24" ht="120" spans="1:10">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="26">
@@ -2976,7 +3045,7 @@
       <c r="G24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="31"/>
+      <c r="H24" s="40"/>
       <c r="I24">
         <f>IF(F8="N",F21+F22-F23,IF(F8="Y",F21+F22-F13,""))</f>
         <v>200000000</v>
@@ -2986,19 +3055,19 @@
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="26">
@@ -3008,22 +3077,22 @@
       <c r="G25" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="31"/>
+      <c r="H25" s="40"/>
     </row>
     <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="26">
@@ -3033,22 +3102,22 @@
       <c r="G26" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="31"/>
+      <c r="H26" s="40"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="26">
@@ -3057,22 +3126,22 @@
       <c r="G27" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="31"/>
+      <c r="H27" s="40"/>
     </row>
     <row r="28" ht="45" spans="1:10">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="26">
@@ -3081,22 +3150,22 @@
       <c r="G28" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="31"/>
+      <c r="H28" s="40"/>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="26">
@@ -3106,44 +3175,44 @@
       <c r="G29" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="31"/>
+      <c r="H29" s="40"/>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="14">
         <v>0</v>
       </c>
       <c r="G30" s="26"/>
-      <c r="H30" s="31"/>
+      <c r="H30" s="40"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="36" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="26">
@@ -3153,22 +3222,22 @@
       <c r="G31" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="31"/>
+      <c r="H31" s="40"/>
     </row>
     <row r="32" ht="60" spans="1:10">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="26">
@@ -3178,22 +3247,22 @@
       <c r="G32" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="31"/>
+      <c r="H32" s="40"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="26">
@@ -3203,22 +3272,22 @@
       <c r="G33" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="31"/>
+      <c r="H33" s="40"/>
     </row>
     <row r="34" ht="30" spans="1:8">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="36" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="26">
@@ -3228,7 +3297,7 @@
       <c r="G34" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="31"/>
+      <c r="H34" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3239,7 +3308,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4190476190476" style="18" customWidth="1"/>
@@ -3249,24 +3318,25 @@
     <col min="5" max="5" width="34.2857142857143" style="19" customWidth="1"/>
     <col min="6" max="6" width="21.2857142857143" style="20" customWidth="1"/>
     <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
-    <col min="8" max="8" width="9.4" customWidth="1"/>
-    <col min="9" max="9" width="21.2857142857143" style="21" customWidth="1"/>
+    <col min="8" max="8" width="9.4" style="22" customWidth="1"/>
+    <col min="9" max="9" width="21.2857142857143" style="20" customWidth="1"/>
+    <col min="10" max="16384" width="9.14285714285714" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="23" t="s">
@@ -3275,12 +3345,12 @@
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="23" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -3297,10 +3367,10 @@
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="26"/>
-      <c r="I2" s="26"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" ht="30" spans="1:10">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="24" t="s">
@@ -3317,10 +3387,10 @@
       </c>
       <c r="F3" s="25"/>
       <c r="G3" s="26"/>
-      <c r="I3" s="26"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="24" t="s">
@@ -3337,10 +3407,10 @@
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="26"/>
-      <c r="I4" s="26"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="24" t="s">
@@ -3357,10 +3427,10 @@
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="26"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" ht="30" spans="1:10">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -3377,10 +3447,10 @@
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="26"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" ht="30" spans="1:10">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="24" t="s">
@@ -3397,10 +3467,10 @@
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="26"/>
-      <c r="I7" s="26"/>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -3421,13 +3491,13 @@
       <c r="G8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="26" t="str">
+      <c r="I8" s="25" t="str">
         <f>F8</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:10">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="24" t="s">
@@ -3446,10 +3516,10 @@
       <c r="G9" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="26"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="24" t="s">
@@ -3465,16 +3535,18 @@
         <v>43</v>
       </c>
       <c r="F10" s="25">
-        <v>100010008</v>
-      </c>
-      <c r="G10" s="26"/>
-      <c r="I10" s="26">
+        <v>20000000</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="25">
         <f>F10</f>
-        <v>100010008</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="24" t="s">
@@ -3491,18 +3563,19 @@
       </c>
       <c r="F11" s="25">
         <f>F10</f>
-        <v>100010008</v>
+        <v>20000000</v>
       </c>
       <c r="G11" s="26"/>
-      <c r="I11" s="26">
-        <v>345452343</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="I11" s="25">
+        <f>F11</f>
+        <v>20000000</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="12" ht="30" spans="1:10">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B12" s="24" t="s">
@@ -3518,49 +3591,42 @@
         <v>51</v>
       </c>
       <c r="F12" s="25">
-        <v>1000000</v>
-      </c>
-      <c r="G12" s="26"/>
-      <c r="I12" s="26">
+        <v>0</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="25">
         <f>F12</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="13" ht="30" spans="1:10">
-      <c r="A13" s="22" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="7"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" s="29">
+        <v>1</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="I13" s="29">
+        <f>F13</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="75" spans="1:10">
+      <c r="A14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B14" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="25">
-        <f>40%*(F10-F12)</f>
-        <v>39604003.2</v>
-      </c>
-      <c r="G13" s="26"/>
-      <c r="I13" s="26">
-        <f>40%*(I11-I12)</f>
-        <v>137780937.2</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="1:10">
-      <c r="A14" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>57</v>
-      </c>
       <c r="C14" s="24" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>55</v>
@@ -3569,137 +3635,139 @@
         <v>43</v>
       </c>
       <c r="F14" s="25">
-        <f>60%*(F10-F12)</f>
-        <v>59406004.8</v>
-      </c>
-      <c r="G14" s="26"/>
-      <c r="I14" s="26">
-        <f>60%*(I10-I12)</f>
-        <v>59406004.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="22" t="s">
+        <f>IF(F13=1,60%*(F10-F12),75%*(F10-F12))</f>
+        <v>12000000</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="25">
+        <f>IF(I13=1,60%*(I10-I12),75%*(I10-I12))</f>
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="15" ht="75" spans="1:10">
+      <c r="A15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="25">
+        <f>IF(F13=1,40%*(F10-F12),25%*(F10-F12))</f>
+        <v>8000000</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="25">
+        <f>IF(I13=1,40%*(I10-I12),25%*(I10-I12))</f>
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B16" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C16" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D16" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="25">
+      <c r="E16" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="25">
         <v>50000000</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G16" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="26">
-        <f>F15</f>
+      <c r="H16" s="30"/>
+      <c r="I16" s="25">
+        <f>F16</f>
         <v>50000000</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="22" t="s">
+    <row r="17" spans="1:10">
+      <c r="A17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B17" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C17" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="30">
-        <v>60000000</v>
-      </c>
-      <c r="G16" s="26" t="s">
+      <c r="E17" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="31">
+        <v>1</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="14">
-        <f>F16</f>
-        <v>60000000</v>
-      </c>
-    </row>
-    <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="22" t="s">
+      <c r="H17" s="30"/>
+      <c r="I17" s="31">
+        <f>F17</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="30" spans="1:10">
+      <c r="A18" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B18" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C18" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D18" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="25">
-        <f>MAX(F15,F16)</f>
-        <v>60000000</v>
-      </c>
-      <c r="G17" s="26" t="s">
+      <c r="E18" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="25">
+        <f>MAX(F16,F17)</f>
+        <v>50000000</v>
+      </c>
+      <c r="G18" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="26">
-        <f>MAX(I15,I16)</f>
-        <v>60000000</v>
-      </c>
-    </row>
-    <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="22" t="s">
+      <c r="H18" s="30"/>
+      <c r="I18" s="25">
+        <f>MAX(I16,I17)</f>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="19" ht="30" spans="1:10">
+      <c r="A19" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B19" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C19" s="24" t="s">
         <v>74</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="25">
-        <v>300000000</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="29"/>
-      <c r="I18" s="26">
-        <f>F18</f>
-        <v>300000000</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>77</v>
       </c>
       <c r="D19" s="27" t="s">
         <v>15</v>
@@ -3708,57 +3776,54 @@
         <v>11</v>
       </c>
       <c r="F19" s="25">
-        <v>100</v>
+        <v>100000000</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="26">
+      <c r="H19" s="30"/>
+      <c r="I19" s="25">
         <f>F19</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="1:10">
+      <c r="A20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="25">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="22" t="s">
+      <c r="G20" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="30"/>
+      <c r="I20" s="25">
+        <f>F20</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:10">
+      <c r="A21" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B21" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C21" s="24" t="s">
         <v>85</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="25">
-        <f>F18</f>
-        <v>300000000</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="26">
-        <v>300450000</v>
-      </c>
-      <c r="J20" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>89</v>
       </c>
       <c r="D21" s="24" t="s">
         <v>86</v>
@@ -3768,323 +3833,358 @@
       </c>
       <c r="F21" s="25">
         <f>F19</f>
-        <v>100</v>
+        <v>100000000</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="26">
-        <v>1000</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="H21" s="32"/>
+      <c r="I21" s="25">
+        <f>F21</f>
+        <v>100000000</v>
+      </c>
+      <c r="J21" s="22" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="22" ht="120" spans="1:10">
-      <c r="A22" s="22" t="s">
-        <v>94</v>
+    <row r="22" ht="30" spans="1:10">
+      <c r="A22" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E22" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="25">
-        <f>IF(F8="N",F18+F19-#REF!,IF(F8="Y",F18+F19-F13,""))</f>
-        <v>260396096.8</v>
+        <f>F20</f>
+        <v>100</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="31"/>
-      <c r="I22" s="26">
-        <f>IF(I8="N",I18+I19-#REF!,IF(I8="Y",I18+I19-I13,""))</f>
-        <v>162219162.8</v>
-      </c>
-    </row>
-    <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="22" t="s">
-        <v>99</v>
+      <c r="H22" s="32"/>
+      <c r="I22" s="25">
+        <f>F22</f>
+        <v>100</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" ht="120" spans="1:10">
+      <c r="A23" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E23" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="25">
-        <f>60%*(F22-F17)</f>
-        <v>120237658.08</v>
+        <f>F19+F20-F14</f>
+        <v>88000100</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="31"/>
-      <c r="I23" s="26">
-        <f>60%*(I22-I17)</f>
-        <v>61331497.68</v>
-      </c>
-    </row>
-    <row r="24" ht="45" spans="1:10">
-      <c r="A24" s="22" t="s">
-        <v>103</v>
+      <c r="H23" s="33"/>
+      <c r="I23" s="25">
+        <f>I21+I22-I14</f>
+        <v>88000100</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:10">
+      <c r="A24" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="E24" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="25">
-        <f>IF(F8="N",75%*F23,IF(F8="Y",100%*F23,""))</f>
-        <v>120237658.08</v>
+        <f>75%*(F23-F18)</f>
+        <v>28500075</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="31"/>
-      <c r="I24" s="26">
-        <f>IF(I8="N",75%*I23,IF(I8="Y",100%*I23,""))</f>
-        <v>61331497.68</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="22" t="s">
+      <c r="H24" s="33"/>
+      <c r="I24" s="25">
+        <f>75%*(I23-I18)</f>
+        <v>28500075</v>
+      </c>
+    </row>
+    <row r="25" ht="45" spans="1:10">
+      <c r="A25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="25">
+        <f>IF(F8="N",75%*F24,IF(F8="Y",100%*F24,""))</f>
+        <v>28500075</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="25">
+        <f>IF(I8="N",75%*I24,IF(I8="Y",100%*I24,""))</f>
+        <v>28500075</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="1:10">
+      <c r="A26" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B26" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C26" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D26" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="25">
-        <v>142919013.51</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="31"/>
-      <c r="I25" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>114</v>
-      </c>
       <c r="E26" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="25">
-        <v>0</v>
+        <v>47639671.17</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H26" s="31"/>
-      <c r="I26" s="26">
+      <c r="H26" s="33"/>
+      <c r="I26" s="25">
+        <f>F26</f>
+        <v>47639671.17</v>
+      </c>
+    </row>
+    <row r="27" ht="45" spans="1:10">
+      <c r="A27" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" ht="30" spans="1:10">
-      <c r="A27" s="22" t="s">
+      <c r="G27" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="33"/>
+      <c r="I27" s="25">
+        <f>F27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="30" spans="1:10">
+      <c r="A28" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B28" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C28" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="25">
-        <f>2*(F25+F26)</f>
-        <v>285838027.02</v>
-      </c>
-      <c r="G27" s="26" t="s">
+      <c r="D28" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="25">
+        <f>3*(F26+F27)</f>
+        <v>142919013.51</v>
+      </c>
+      <c r="G28" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H27" s="31"/>
-      <c r="I27" s="26">
-        <f>2*(I25+I26)</f>
+      <c r="H28" s="33"/>
+      <c r="I28" s="25">
+        <f>3*(I26+I27)</f>
+        <v>142919013.51</v>
+      </c>
+    </row>
+    <row r="29" ht="30" spans="1:10">
+      <c r="A29" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="31">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" ht="30" spans="1:10">
-      <c r="A28" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="30">
+      <c r="G29" s="26"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="31">
         <v>0</v>
       </c>
-      <c r="G28" s="26"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="22" t="s">
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B30" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C30" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D30" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E30" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="25">
-        <f>F27-F28</f>
-        <v>285838027.02</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="31"/>
-      <c r="I29" s="26">
-        <f>I27-I28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="60" spans="1:10">
-      <c r="A30" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>11</v>
-      </c>
       <c r="F30" s="25">
-        <f>IF(F24&lt;=F29,F24,F29)</f>
-        <v>120237658.08</v>
+        <f>F28-F29</f>
+        <v>142919013.51</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="31"/>
-      <c r="I30" s="26">
-        <f>IF(I24&lt;=I29,I24,I29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="22" t="s">
-        <v>130</v>
+      <c r="H30" s="33"/>
+      <c r="I30" s="25">
+        <f>I28-I29</f>
+        <v>142919013.51</v>
+      </c>
+    </row>
+    <row r="31" ht="60" spans="1:10">
+      <c r="A31" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E31" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="25">
-        <f>F29-F30</f>
-        <v>165600368.94</v>
+        <f>IF(F25&lt;=F30,F25,F30)</f>
+        <v>28500075</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="31"/>
-      <c r="I31" s="26">
-        <f>I29-I30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="30" spans="1:10">
-      <c r="A32" s="22" t="s">
-        <v>134</v>
+      <c r="H31" s="33"/>
+      <c r="I31" s="25">
+        <f>IF(I25&lt;=I30,I25,I30)</f>
+        <v>28500075</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E32" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F32" s="25"/>
+      <c r="F32" s="25">
+        <f>F30-F31</f>
+        <v>114418938.51</v>
+      </c>
       <c r="G32" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="31"/>
-      <c r="I32" s="26"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="25">
+        <f>I30-I31</f>
+        <v>114418938.51</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="1:9">
+      <c r="A33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="25"/>
+      <c r="G33" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" s="33"/>
+      <c r="I33" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4142,7 +4242,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>11</v>
@@ -4158,7 +4258,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>15</v>
@@ -4207,7 +4307,7 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="J5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K5" s="11"/>
     </row>
@@ -4219,7 +4319,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>15</v>
@@ -4230,7 +4330,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="J6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K6" s="12"/>
     </row>
@@ -4239,10 +4339,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>15</v>
@@ -4301,7 +4401,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>42</v>
@@ -4355,10 +4455,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>55</v>
@@ -4377,7 +4477,7 @@
         <v>57</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>55</v>
@@ -4396,7 +4496,7 @@
         <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>15</v>
@@ -4408,7 +4508,7 @@
         <v>100000000</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15">
@@ -4424,10 +4524,10 @@
         <v>76</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>11</v>
@@ -4436,7 +4536,7 @@
         <v>100000000</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H16" s="11"/>
       <c r="I16">
@@ -4452,10 +4552,10 @@
         <v>79</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>11</v>
@@ -4475,16 +4575,16 @@
         <v>72</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F18" s="10">
         <v>80000000</v>
@@ -4500,16 +4600,16 @@
         <v>75</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>86</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F19" s="10">
         <f>F18</f>
@@ -4521,24 +4621,24 @@
         <v>80000000</v>
       </c>
       <c r="J19" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" ht="45" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F20" s="10">
         <f>40%*F18</f>
@@ -4552,19 +4652,19 @@
     </row>
     <row r="21" ht="30" spans="1:10">
       <c r="A21" s="9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F21" s="10">
         <f>60%*F18</f>
@@ -4581,16 +4681,16 @@
         <v>83</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -4600,16 +4700,16 @@
         <v>87</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -4634,7 +4734,7 @@
         <v>50000000</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24">
@@ -4644,10 +4744,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>65</v>
@@ -4673,13 +4773,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>11</v>
@@ -4701,7 +4801,7 @@
         <v>69</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>11</v>
@@ -4722,13 +4822,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>11</v>
@@ -4748,13 +4848,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>11</v>
@@ -4774,10 +4874,10 @@
         <v>115</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>15</v>
@@ -4789,7 +4889,7 @@
         <v>62999995.5</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I30">
         <f t="shared" ref="I30:I35" si="0">F30</f>
@@ -4801,13 +4901,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>11</v>
@@ -4842,7 +4942,7 @@
         <v>5487293.76</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I32">
         <f t="shared" si="0"/>
@@ -4869,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -4887,7 +4987,7 @@
         <v>117</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>11</v>
@@ -4897,7 +4997,7 @@
         <v>10974587.52</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I34">
         <f t="shared" si="0"/>
@@ -4924,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I35">
         <f t="shared" si="0"/>
@@ -4933,7 +5033,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="9" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>123</v>
@@ -4942,7 +5042,7 @@
         <v>123</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>125</v>
@@ -4952,7 +5052,7 @@
         <v>10974587.52</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I36">
         <f>I34-I35</f>
@@ -4961,16 +5061,16 @@
     </row>
     <row r="37" ht="45" spans="1:9">
       <c r="A37" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>11</v>
@@ -4987,7 +5087,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>131</v>
@@ -4996,7 +5096,7 @@
         <v>132</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>11</v>
@@ -5013,7 +5113,7 @@
     </row>
     <row r="39" ht="30" spans="1:9">
       <c r="A39" s="9" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>135</v>
@@ -5022,7 +5122,7 @@
         <v>136</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>11</v>
@@ -5085,7 +5185,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>11</v>
@@ -5101,7 +5201,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>15</v>
@@ -5150,7 +5250,7 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="J5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K5" s="11"/>
     </row>
@@ -5162,7 +5262,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>15</v>
@@ -5173,7 +5273,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="J6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K6" s="12"/>
     </row>
@@ -5182,10 +5282,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>15</v>
@@ -5244,7 +5344,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>42</v>
@@ -5298,10 +5398,10 @@
         <v>52</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>55</v>
@@ -5320,7 +5420,7 @@
         <v>57</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>55</v>
@@ -5339,7 +5439,7 @@
         <v>73</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>15</v>
@@ -5351,7 +5451,7 @@
         <v>400000000</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -5363,10 +5463,10 @@
         <v>76</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>11</v>
@@ -5375,7 +5475,7 @@
         <v>5000000</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -5387,10 +5487,10 @@
         <v>79</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>11</v>
@@ -5404,16 +5504,16 @@
         <v>72</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -5423,54 +5523,54 @@
         <v>75</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>86</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
     <row r="20" ht="45" spans="1:8">
       <c r="A20" s="9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
     <row r="21" ht="30" spans="1:8">
       <c r="A21" s="9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -5480,16 +5580,16 @@
         <v>83</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -5499,16 +5599,16 @@
         <v>87</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -5533,16 +5633,16 @@
         <v>150000000</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>65</v>
@@ -5564,13 +5664,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>11</v>
@@ -5590,7 +5690,7 @@
         <v>69</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>11</v>
@@ -5607,13 +5707,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>11</v>
@@ -5626,13 +5726,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>11</v>
@@ -5645,10 +5745,10 @@
         <v>115</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>15</v>
@@ -5664,13 +5764,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>11</v>
@@ -5727,7 +5827,7 @@
         <v>117</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>11</v>
@@ -5756,7 +5856,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="9" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>123</v>
@@ -5765,7 +5865,7 @@
         <v>123</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>125</v>
@@ -5775,16 +5875,16 @@
     </row>
     <row r="37" ht="45" spans="1:7">
       <c r="A37" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>127</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>11</v>
@@ -5794,7 +5894,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>131</v>
@@ -5803,7 +5903,7 @@
         <v>132</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>11</v>
@@ -5813,7 +5913,7 @@
     </row>
     <row r="39" ht="30" spans="1:7">
       <c r="A39" s="9" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>135</v>
@@ -5822,7 +5922,7 @@
         <v>136</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>11</v>
@@ -5848,13 +5948,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:3">
@@ -5862,10 +5962,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:3">
@@ -5873,10 +5973,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" ht="30" spans="1:3">
@@ -5884,10 +5984,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:3">
@@ -5895,10 +5995,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:3">
@@ -5906,10 +6006,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5917,10 +6017,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5928,10 +6028,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5939,10 +6039,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:3">
@@ -5950,10 +6050,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/MSME/MSME intrim claim calculations.xlsx
+++ b/MSME/MSME intrim claim calculations.xlsx
@@ -534,6 +534,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Amount recovered through OTS ( Proportionate amount of NCGTC recovery ) – 40% of 9A-9C for MLI / 40% of 9B-9C for NCGTC.
 </t>
     </r>
@@ -550,6 +557,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Amount recovered through OTS retained by MLI – 60% of 9A-9C for MLI / 60% of 9B-9C for NCGTC.
 </t>
     </r>
@@ -3535,14 +3549,14 @@
         <v>43</v>
       </c>
       <c r="F10" s="25">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>34</v>
       </c>
       <c r="I10" s="25">
         <f>F10</f>
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
@@ -3563,12 +3577,12 @@
       </c>
       <c r="F11" s="25">
         <f>F10</f>
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="G11" s="26"/>
       <c r="I11" s="25">
         <f>F11</f>
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="J11" s="22" t="s">
         <v>141</v>
@@ -3610,12 +3624,12 @@
         <v>142</v>
       </c>
       <c r="F13" s="29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="26"/>
       <c r="I13" s="29">
         <f>F13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="75" spans="1:10">
@@ -3636,14 +3650,14 @@
       </c>
       <c r="F14" s="25">
         <f>IF(F13=1,60%*(F10-F12),75%*(F10-F12))</f>
-        <v>12000000</v>
+        <v>7500000</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="25">
         <f>IF(I13=1,60%*(I10-I12),75%*(I10-I12))</f>
-        <v>12000000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:10">
@@ -3664,14 +3678,14 @@
       </c>
       <c r="F15" s="25">
         <f>IF(F13=1,40%*(F10-F12),25%*(F10-F12))</f>
-        <v>8000000</v>
+        <v>2500000</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="25">
         <f>IF(I13=1,40%*(I10-I12),25%*(I10-I12))</f>
-        <v>8000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3897,7 +3911,7 @@
       </c>
       <c r="F23" s="25">
         <f>F19+F20-F14</f>
-        <v>88000100</v>
+        <v>92500100</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>71</v>
@@ -3905,7 +3919,7 @@
       <c r="H23" s="33"/>
       <c r="I23" s="25">
         <f>I21+I22-I14</f>
-        <v>88000100</v>
+        <v>92500100</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:10">
@@ -3926,7 +3940,7 @@
       </c>
       <c r="F24" s="25">
         <f>75%*(F23-F18)</f>
-        <v>28500075</v>
+        <v>31875075</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>71</v>
@@ -3934,7 +3948,7 @@
       <c r="H24" s="33"/>
       <c r="I24" s="25">
         <f>75%*(I23-I18)</f>
-        <v>28500075</v>
+        <v>31875075</v>
       </c>
     </row>
     <row r="25" ht="45" spans="1:10">
@@ -3955,7 +3969,7 @@
       </c>
       <c r="F25" s="25">
         <f>IF(F8="N",75%*F24,IF(F8="Y",100%*F24,""))</f>
-        <v>28500075</v>
+        <v>31875075</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>71</v>
@@ -3963,7 +3977,7 @@
       <c r="H25" s="33"/>
       <c r="I25" s="25">
         <f>IF(I8="N",75%*I24,IF(I8="Y",100%*I24,""))</f>
-        <v>28500075</v>
+        <v>31875075</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:10">
@@ -4123,7 +4137,7 @@
       </c>
       <c r="F31" s="25">
         <f>IF(F25&lt;=F30,F25,F30)</f>
-        <v>28500075</v>
+        <v>31875075</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>71</v>
@@ -4131,7 +4145,7 @@
       <c r="H31" s="33"/>
       <c r="I31" s="25">
         <f>IF(I25&lt;=I30,I25,I30)</f>
-        <v>28500075</v>
+        <v>31875075</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -4152,7 +4166,7 @@
       </c>
       <c r="F32" s="25">
         <f>F30-F31</f>
-        <v>114418938.51</v>
+        <v>111043938.51</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>71</v>
@@ -4160,7 +4174,7 @@
       <c r="H32" s="33"/>
       <c r="I32" s="25">
         <f>I30-I31</f>
-        <v>114418938.51</v>
+        <v>111043938.51</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:9">

--- a/MSME/MSME intrim claim calculations.xlsx
+++ b/MSME/MSME intrim claim calculations.xlsx
@@ -1877,7 +1877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1962,17 +1962,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2532,30 +2541,30 @@
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="34" customWidth="1"/>
-    <col min="2" max="2" width="38" style="34" customWidth="1"/>
-    <col min="3" max="3" width="64" style="34" customWidth="1"/>
-    <col min="4" max="4" width="48.2857142857143" style="34" customWidth="1"/>
-    <col min="5" max="5" width="34.2857142857143" style="34" customWidth="1"/>
+    <col min="1" max="1" width="6.71428571428571" style="37" customWidth="1"/>
+    <col min="2" max="2" width="38" style="37" customWidth="1"/>
+    <col min="3" max="3" width="64" style="37" customWidth="1"/>
+    <col min="4" max="4" width="48.2857142857143" style="37" customWidth="1"/>
+    <col min="5" max="5" width="34.2857142857143" style="37" customWidth="1"/>
     <col min="6" max="6" width="21.2857142857143" style="21" customWidth="1"/>
     <col min="7" max="7" width="16.5714285714286" style="21" customWidth="1"/>
     <col min="8" max="9" width="15.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
@@ -2566,133 +2575,133 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
     </row>
     <row r="3" ht="30" spans="1:8">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
     <row r="6" ht="30" spans="1:8">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
     <row r="7" ht="30" spans="1:8">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="26" t="s">
@@ -2703,133 +2712,133 @@
       </c>
     </row>
     <row r="9" ht="30" spans="1:8">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="41" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="41" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
     </row>
     <row r="11" ht="30" spans="1:8">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="41" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
     <row r="12" ht="30" spans="1:8">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="41" t="s">
         <v>51</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
     </row>
     <row r="13" ht="30" spans="1:8">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="41" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
     </row>
     <row r="14" ht="30" spans="1:8">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="41" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="26">
@@ -2838,22 +2847,22 @@
       <c r="G15" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="39"/>
+      <c r="H15" s="42"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="14">
@@ -2862,22 +2871,22 @@
       <c r="G16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="39"/>
+      <c r="H16" s="42"/>
     </row>
     <row r="17" ht="30" spans="1:10">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="26">
@@ -2887,22 +2896,22 @@
       <c r="G17" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="39"/>
+      <c r="H17" s="42"/>
     </row>
     <row r="18" ht="30" spans="1:10">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="26">
@@ -2911,22 +2920,22 @@
       <c r="G18" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="39"/>
+      <c r="H18" s="42"/>
     </row>
     <row r="19" ht="30" spans="1:10">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="26">
@@ -2935,22 +2944,22 @@
       <c r="G19" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="39"/>
+      <c r="H19" s="42"/>
     </row>
     <row r="20" ht="30" spans="1:10">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F20" s="14">
@@ -2959,22 +2968,22 @@
       <c r="G20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="39"/>
+      <c r="H20" s="42"/>
     </row>
     <row r="21" ht="30" spans="1:10">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="26">
@@ -2987,19 +2996,19 @@
       <c r="H21" s="12"/>
     </row>
     <row r="22" ht="30" spans="1:10">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="26">
@@ -3012,19 +3021,19 @@
       <c r="H22" s="12"/>
     </row>
     <row r="23" ht="30" spans="1:10">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="39" t="s">
         <v>93</v>
       </c>
       <c r="F23" s="26">
@@ -3037,19 +3046,19 @@
       <c r="H23" s="12"/>
     </row>
     <row r="24" ht="120" spans="1:10">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="26">
@@ -3059,7 +3068,7 @@
       <c r="G24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="40"/>
+      <c r="H24" s="43"/>
       <c r="I24">
         <f>IF(F8="N",F21+F22-F23,IF(F8="Y",F21+F22-F13,""))</f>
         <v>200000000</v>
@@ -3069,19 +3078,19 @@
       </c>
     </row>
     <row r="25" ht="30" spans="1:10">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="36" t="s">
+      <c r="E25" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="26">
@@ -3091,22 +3100,22 @@
       <c r="G25" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="40"/>
+      <c r="H25" s="43"/>
     </row>
     <row r="26" ht="45" spans="1:10">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="26">
@@ -3116,22 +3125,22 @@
       <c r="G26" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="40"/>
+      <c r="H26" s="43"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="26">
@@ -3140,22 +3149,22 @@
       <c r="G27" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="40"/>
+      <c r="H27" s="43"/>
     </row>
     <row r="28" ht="45" spans="1:10">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="36" t="s">
+      <c r="E28" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="26">
@@ -3164,22 +3173,22 @@
       <c r="G28" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="40"/>
+      <c r="H28" s="43"/>
     </row>
     <row r="29" ht="30" spans="1:10">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="26">
@@ -3189,44 +3198,44 @@
       <c r="G29" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H29" s="40"/>
+      <c r="H29" s="43"/>
     </row>
     <row r="30" ht="30" spans="1:10">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="D30" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="E30" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="14">
         <v>0</v>
       </c>
       <c r="G30" s="26"/>
-      <c r="H30" s="40"/>
+      <c r="H30" s="43"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="36" t="s">
+      <c r="B31" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="36" t="s">
+      <c r="E31" s="39" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="26">
@@ -3236,22 +3245,22 @@
       <c r="G31" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="40"/>
+      <c r="H31" s="43"/>
     </row>
     <row r="32" ht="60" spans="1:10">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="36" t="s">
+      <c r="E32" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="26">
@@ -3261,22 +3270,22 @@
       <c r="G32" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="40"/>
+      <c r="H32" s="43"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="26">
@@ -3286,22 +3295,22 @@
       <c r="G33" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="40"/>
+      <c r="H33" s="43"/>
     </row>
     <row r="34" ht="30" spans="1:8">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="36" t="s">
+      <c r="E34" s="39" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="26">
@@ -3311,7 +3320,7 @@
       <c r="G34" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="40"/>
+      <c r="H34" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3499,13 +3508,14 @@
       <c r="E8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="25" t="str">
+      <c r="H8" s="29"/>
+      <c r="I8" s="28" t="str">
         <f>F8</f>
         <v>Y</v>
       </c>
@@ -3523,7 +3533,7 @@
       <c r="D9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="30" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="25"/>
@@ -3545,18 +3555,18 @@
       <c r="D10" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="30" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="25">
-        <v>10000000</v>
+        <v>3100000</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>34</v>
       </c>
       <c r="I10" s="25">
         <f>F10</f>
-        <v>10000000</v>
+        <v>3100000</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:10">
@@ -3572,19 +3582,18 @@
       <c r="D11" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="30" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="25">
         <f>F10</f>
-        <v>10000000</v>
+        <v>3100000</v>
       </c>
       <c r="G11" s="26"/>
-      <c r="I11" s="25">
-        <f>F11</f>
-        <v>10000000</v>
-      </c>
-      <c r="J11" s="22" t="s">
+      <c r="I11" s="31">
+        <v>4100000</v>
+      </c>
+      <c r="J11" s="32" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3601,18 +3610,18 @@
       <c r="D12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="30" t="s">
         <v>51</v>
       </c>
       <c r="F12" s="25">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>34</v>
       </c>
       <c r="I12" s="25">
         <f>F12</f>
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3620,16 +3629,16 @@
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="29">
-        <v>2</v>
+      <c r="F13" s="33">
+        <v>1</v>
       </c>
       <c r="G13" s="26"/>
-      <c r="I13" s="29">
+      <c r="I13" s="33">
         <f>F13</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="75" spans="1:10">
@@ -3645,19 +3654,19 @@
       <c r="D14" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="30" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="25">
         <f>IF(F13=1,60%*(F10-F12),75%*(F10-F12))</f>
-        <v>7500000</v>
+        <v>1620000</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="25">
         <f>IF(I13=1,60%*(I10-I12),75%*(I10-I12))</f>
-        <v>7500000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:10">
@@ -3673,19 +3682,19 @@
       <c r="D15" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="30" t="s">
         <v>43</v>
       </c>
       <c r="F15" s="25">
         <f>IF(F13=1,40%*(F10-F12),25%*(F10-F12))</f>
-        <v>2500000</v>
+        <v>1080000</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="25">
         <f>IF(I13=1,40%*(I10-I12),25%*(I10-I12))</f>
-        <v>2500000</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3710,7 +3719,7 @@
       <c r="G16" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="30"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="25">
         <f>F16</f>
         <v>50000000</v>
@@ -3738,7 +3747,7 @@
       <c r="G17" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="30"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="31">
         <f>F17</f>
         <v>1</v>
@@ -3767,7 +3776,7 @@
       <c r="G18" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H18" s="30"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="25">
         <f>MAX(I16,I17)</f>
         <v>50000000</v>
@@ -3790,15 +3799,15 @@
         <v>11</v>
       </c>
       <c r="F19" s="25">
-        <v>100000000</v>
+        <v>300000000</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="30"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="25">
         <f>F19</f>
-        <v>100000000</v>
+        <v>300000000</v>
       </c>
     </row>
     <row r="20" ht="30" spans="1:10">
@@ -3823,7 +3832,7 @@
       <c r="G20" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H20" s="30"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="25">
         <f>F20</f>
         <v>100</v>
@@ -3847,17 +3856,16 @@
       </c>
       <c r="F21" s="25">
         <f>F19</f>
-        <v>100000000</v>
+        <v>300000000</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="25">
-        <f>F21</f>
-        <v>100000000</v>
-      </c>
-      <c r="J21" s="22" t="s">
+      <c r="H21" s="35"/>
+      <c r="I21" s="31">
+        <v>400000000</v>
+      </c>
+      <c r="J21" s="32" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3884,12 +3892,11 @@
       <c r="G22" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="32"/>
-      <c r="I22" s="25">
-        <f>F22</f>
-        <v>100</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="H22" s="35"/>
+      <c r="I22" s="31">
+        <v>1000</v>
+      </c>
+      <c r="J22" s="32" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3911,15 +3918,15 @@
       </c>
       <c r="F23" s="25">
         <f>F19+F20-F14</f>
-        <v>92500100</v>
+        <v>298380100</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="33"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="25">
         <f>I21+I22-I14</f>
-        <v>92500100</v>
+        <v>398381000</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:10">
@@ -3940,15 +3947,15 @@
       </c>
       <c r="F24" s="25">
         <f>75%*(F23-F18)</f>
-        <v>31875075</v>
+        <v>186285075</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="33"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="25">
         <f>75%*(I23-I18)</f>
-        <v>31875075</v>
+        <v>261285750</v>
       </c>
     </row>
     <row r="25" ht="45" spans="1:10">
@@ -3969,15 +3976,15 @@
       </c>
       <c r="F25" s="25">
         <f>IF(F8="N",75%*F24,IF(F8="Y",100%*F24,""))</f>
-        <v>31875075</v>
+        <v>186285075</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="33"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="25">
         <f>IF(I8="N",75%*I24,IF(I8="Y",100%*I24,""))</f>
-        <v>31875075</v>
+        <v>261285750</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:10">
@@ -3997,15 +4004,15 @@
         <v>11</v>
       </c>
       <c r="F26" s="25">
-        <v>47639671.17</v>
+        <v>26550000</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H26" s="33"/>
+      <c r="H26" s="36"/>
       <c r="I26" s="25">
         <f>F26</f>
-        <v>47639671.17</v>
+        <v>26550000</v>
       </c>
     </row>
     <row r="27" ht="45" spans="1:10">
@@ -4030,7 +4037,7 @@
       <c r="G27" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="33"/>
+      <c r="H27" s="36"/>
       <c r="I27" s="25">
         <f>F27</f>
         <v>0</v>
@@ -4054,15 +4061,15 @@
       </c>
       <c r="F28" s="25">
         <f>3*(F26+F27)</f>
-        <v>142919013.51</v>
+        <v>79650000</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H28" s="33"/>
+      <c r="H28" s="36"/>
       <c r="I28" s="25">
         <f>3*(I26+I27)</f>
-        <v>142919013.51</v>
+        <v>79650000</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:10">
@@ -4085,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="26"/>
-      <c r="H29" s="33"/>
+      <c r="H29" s="36"/>
       <c r="I29" s="31">
         <v>0</v>
       </c>
@@ -4108,15 +4115,15 @@
       </c>
       <c r="F30" s="25">
         <f>F28-F29</f>
-        <v>142919013.51</v>
+        <v>79650000</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="33"/>
+      <c r="H30" s="36"/>
       <c r="I30" s="25">
         <f>I28-I29</f>
-        <v>142919013.51</v>
+        <v>79650000</v>
       </c>
     </row>
     <row r="31" ht="60" spans="1:10">
@@ -4137,15 +4144,15 @@
       </c>
       <c r="F31" s="25">
         <f>IF(F25&lt;=F30,F25,F30)</f>
-        <v>31875075</v>
+        <v>79650000</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="33"/>
+      <c r="H31" s="36"/>
       <c r="I31" s="25">
         <f>IF(I25&lt;=I30,I25,I30)</f>
-        <v>31875075</v>
+        <v>79650000</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -4166,15 +4173,15 @@
       </c>
       <c r="F32" s="25">
         <f>F30-F31</f>
-        <v>111043938.51</v>
+        <v>0</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="33"/>
+      <c r="H32" s="36"/>
       <c r="I32" s="25">
         <f>I30-I31</f>
-        <v>111043938.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:9">
@@ -4197,7 +4204,7 @@
       <c r="G33" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="33"/>
+      <c r="H33" s="36"/>
       <c r="I33" s="25"/>
     </row>
   </sheetData>
